--- a/test.xlsx
+++ b/test.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="18431"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WorkBench\Robotics\motor-driver\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkBench\Robotics\motor-driver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D571E1-41BC-419E-B376-06496B61923F}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072" activeTab="2" xr2:uid="{5C0E2255-2C1D-4FA3-B226-CB198C38E820}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9075" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="old" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet11" sheetId="12" r:id="rId1"/>
+    <sheet name="Sheet10" sheetId="11" r:id="rId2"/>
+    <sheet name="Sheet11 (2)" sheetId="13" r:id="rId3"/>
+    <sheet name="Sheet13" sheetId="14" r:id="rId4"/>
+    <sheet name="Sheet14" sheetId="15" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="179017"/>
+  <calcPr calcId="171027"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,11 +28,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>pos</t>
+  </si>
+  <si>
+    <t>vel</t>
+  </si>
+  <si>
+    <t>d_pos</t>
+  </si>
+  <si>
+    <t>d^2_pos</t>
+  </si>
+  <si>
+    <t>d_v</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -147,273 +164,57 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$A$1:$A$88</c:f>
+              <c:f>Sheet11!$A$1:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="88"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>9</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>39</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>87</c:v>
+                  <c:v>139</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>156</c:v>
+                  <c:v>314</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>244</c:v>
+                  <c:v>559</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>351</c:v>
+                  <c:v>873</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>478</c:v>
+                  <c:v>1257</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>625</c:v>
+                  <c:v>1711</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>791</c:v>
+                  <c:v>2288</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>976</c:v>
+                  <c:v>2742</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1181</c:v>
+                  <c:v>3126</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1406</c:v>
+                  <c:v>3441</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1650</c:v>
+                  <c:v>3685</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1914</c:v>
+                  <c:v>3860</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2197</c:v>
+                  <c:v>3965</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2500</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2822</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>3164</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>3525</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>3906</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>4306</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>4726</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>5166</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>5625</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>6093</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>6562</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>7031</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>7500</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>7968</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>8437</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>8906</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>9375</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>9843</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>10312</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>10781</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>11250</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>11718</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>12187</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>12656</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>13125</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>13593</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>14062</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>14531</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>15468</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>15937</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>16406</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>16875</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>17343</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>17812</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>18281</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>18750</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>19218</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>19687</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>20156</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>20625</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>21093</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>21562</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>22031</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>22500</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>22968</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>23437</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>23906</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>24375</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>24833</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>25273</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>25693</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>26093</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>26474</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>26835</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>27177</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>27500</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>27802</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>28085</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>28349</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>28593</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>28818</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>29023</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>29208</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>29375</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>29521</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>29648</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>29755</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>29843</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>29912</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>29960</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>29990</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>30000</c:v>
+                  <c:v>4000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -421,7 +222,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C4BE-467B-B312-7EDC2A4511D5}"/>
+              <c16:uniqueId val="{00000000-D6FE-4DE2-8239-0E4FF28711B3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -442,272 +243,56 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$1:$B$88</c:f>
+              <c:f>Sheet11!$B$1:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="88"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>625</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1250</c:v>
+                  <c:v>1118</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1875</c:v>
+                  <c:v>2236</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2500</c:v>
+                  <c:v>3354</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3125</c:v>
+                  <c:v>4472</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3750</c:v>
+                  <c:v>5590</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4375</c:v>
+                  <c:v>6708</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5000</c:v>
+                  <c:v>7826</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5625</c:v>
+                  <c:v>7827</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6250</c:v>
+                  <c:v>6709</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>6875</c:v>
+                  <c:v>5591</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7500</c:v>
+                  <c:v>4473</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8125</c:v>
+                  <c:v>3355</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8750</c:v>
+                  <c:v>2237</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9375</c:v>
+                  <c:v>1119</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>10625</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>11250</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>11875</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>12500</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>13125</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>13750</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>14375</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>14375</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>13750</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>13125</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>12500</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>11875</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>11250</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>10625</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>9375</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>8750</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>8125</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>7500</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>6875</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>6250</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>5625</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>5000</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>4375</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>3750</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>3125</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>2500</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>1875</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>1250</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>625</c:v>
-                </c:pt>
-                <c:pt idx="87">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -716,7 +301,232 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C4BE-467B-B312-7EDC2A4511D5}"/>
+              <c16:uniqueId val="{00000001-D6FE-4DE2-8239-0E4FF28711B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet11!$C$1:$C$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="1">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-1119</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D6FE-4DE2-8239-0E4FF28711B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet11!$D$1:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>314</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>384</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>454</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>577</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>454</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>384</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>315</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>35</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-D6FE-4DE2-8239-0E4FF28711B3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet11!$E$1:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="2">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>123</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-123</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-70</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-69</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-71</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-69</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-70</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-70</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-D6FE-4DE2-8239-0E4FF28711B3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -729,11 +539,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="429957528"/>
-        <c:axId val="429958512"/>
+        <c:axId val="425025048"/>
+        <c:axId val="425020128"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="429957528"/>
+        <c:axId val="425025048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -775,7 +585,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="429958512"/>
+        <c:crossAx val="425020128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -783,7 +593,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="429958512"/>
+        <c:axId val="425020128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -834,7 +644,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="429957528"/>
+        <c:crossAx val="425025048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -879,13 +689,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -988,141 +791,57 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$A$1:$A$44</c:f>
+              <c:f>'Sheet11 (2)'!$A$1:$A$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>39</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>156</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>351</c:v>
+                  <c:v>139</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>625</c:v>
+                  <c:v>314</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>976</c:v>
+                  <c:v>559</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1406</c:v>
+                  <c:v>873</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1914</c:v>
+                  <c:v>1257</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2500</c:v>
+                  <c:v>1711</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3164</c:v>
+                  <c:v>1764</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3906</c:v>
+                  <c:v>2288</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>4726</c:v>
+                  <c:v>2742</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>5625</c:v>
+                  <c:v>3126</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6562</c:v>
+                  <c:v>3441</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7500</c:v>
+                  <c:v>3685</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8437</c:v>
+                  <c:v>3860</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9375</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>10312</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>11250</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>12187</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>13125</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>14062</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>15937</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>16875</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>17812</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>18750</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>19687</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>20625</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>21562</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>22500</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>23437</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>24375</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>25273</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>26093</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>26835</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>27500</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>28085</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>28593</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>29023</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>29375</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>29648</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>29843</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>29960</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>30000</c:v>
+                  <c:v>3965</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1130,7 +849,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-54AB-4802-B6DB-93E3609C73D3}"/>
+              <c16:uniqueId val="{00000000-5CE2-4E00-99F6-5DE11745CA1B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1151,141 +870,57 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Sheet2!$B$1:$B$44</c:f>
+              <c:f>'Sheet11 (2)'!$B$1:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>1250</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2500</c:v>
+                  <c:v>1118</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3750</c:v>
+                  <c:v>2236</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>3354</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6250</c:v>
+                  <c:v>4472</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7500</c:v>
+                  <c:v>5590</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8750</c:v>
+                  <c:v>6708</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10000</c:v>
+                  <c:v>7826</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11250</c:v>
+                  <c:v>8945</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12500</c:v>
+                  <c:v>7827</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13750</c:v>
+                  <c:v>6709</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>15000</c:v>
+                  <c:v>5591</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>15000</c:v>
+                  <c:v>4473</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>15000</c:v>
+                  <c:v>3355</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15000</c:v>
+                  <c:v>2237</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>13750</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>12500</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>11250</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>8750</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>7500</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>6250</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>5000</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>3750</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2500</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1250</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>0</c:v>
+                  <c:v>1119</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1293,7 +928,232 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-54AB-4802-B6DB-93E3609C73D3}"/>
+              <c16:uniqueId val="{00000001-5CE2-4E00-99F6-5DE11745CA1B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet11 (2)'!$C$1:$C$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="1">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1119</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1118</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-1118</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5CE2-4E00-99F6-5DE11745CA1B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet11 (2)'!$D$1:$D$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>314</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>384</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>454</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>524</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>454</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>384</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>315</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>244</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>105</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-5CE2-4E00-99F6-5DE11745CA1B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet11 (2)'!$E$1:$E$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="16"/>
+                <c:pt idx="2">
+                  <c:v>71</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-401</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>471</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-70</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-70</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-69</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-71</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-69</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-70</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-5CE2-4E00-99F6-5DE11745CA1B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1306,11 +1166,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="761883440"/>
-        <c:axId val="761889672"/>
+        <c:axId val="425025048"/>
+        <c:axId val="425020128"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="761883440"/>
+        <c:axId val="425025048"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1352,7 +1212,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="761889672"/>
+        <c:crossAx val="425020128"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1360,7 +1220,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="761889672"/>
+        <c:axId val="425020128"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1411,7 +1271,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="761883440"/>
+        <c:crossAx val="425025048"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1456,13 +1316,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -1565,10 +1418,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>old!$A$1:$A$44</c:f>
+              <c:f>Sheet13!$A$3:$A$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>39</c:v>
                 </c:pt>
@@ -1579,127 +1432,16 @@
                   <c:v>351</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>625</c:v>
+                  <c:v>586</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>976</c:v>
+                  <c:v>781</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1406</c:v>
+                  <c:v>898</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1914</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2500</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3164</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3906</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4726</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5625</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>6562</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>7500</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8437</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>9375</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>10312</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>11250</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>12187</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>13125</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>14062</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>15937</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>16875</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>17812</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>18750</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>19687</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>20625</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>21562</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>22500</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>23437</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>24375</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>25273</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>26093</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>26835</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>27500</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>28085</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>28593</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>29023</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>29375</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>29648</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>29843</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>29960</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>30000</c:v>
+                  <c:v>1000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1707,7 +1449,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4A95-4CDE-AEB8-1CCC3157A1EC}"/>
+              <c16:uniqueId val="{00000000-E2A9-42E2-8C2B-A94C338C2909}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1728,10 +1470,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>old!$B$1:$B$44</c:f>
+              <c:f>Sheet13!$B$3:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="44"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
                   <c:v>1250</c:v>
                 </c:pt>
@@ -1742,126 +1484,15 @@
                   <c:v>3750</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5000</c:v>
+                  <c:v>3750</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6250</c:v>
+                  <c:v>2500</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7500</c:v>
+                  <c:v>1250</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8750</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>11250</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>12500</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>13750</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>15000</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>13750</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>12500</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>11250</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>8750</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>7500</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>6250</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>5000</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>3750</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2500</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>1250</c:v>
-                </c:pt>
-                <c:pt idx="43">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1870,7 +1501,160 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4A95-4CDE-AEB8-1CCC3157A1EC}"/>
+              <c16:uniqueId val="{00000001-E2A9-42E2-8C2B-A94C338C2909}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet13!$C$3:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>117</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>102</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E2A9-42E2-8C2B-A94C338C2909}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet13!$D$3:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="1">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-78</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-E2A9-42E2-8C2B-A94C338C2909}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet13!$E$3:$E$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1250</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1250</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1250</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-E2A9-42E2-8C2B-A94C338C2909}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1883,11 +1667,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="763712520"/>
-        <c:axId val="763712848"/>
+        <c:axId val="419704784"/>
+        <c:axId val="419705112"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="763712520"/>
+        <c:axId val="419704784"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1929,7 +1713,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="763712848"/>
+        <c:crossAx val="419705112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1937,7 +1721,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="763712848"/>
+        <c:axId val="419705112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1988,7 +1772,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="763712520"/>
+        <c:crossAx val="419704784"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2033,13 +1817,444 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet14!$A$1:$A$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10351</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10781</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11289</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11875</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12539</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13281</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14101</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14929</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>15695</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>16398</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>17038</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17616</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18131</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>18583</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18973</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>19301</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19565</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19767</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>19907</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>19984</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>20000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B144-412D-A091-CD215F21A09C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet14!$B$1:$B$22</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="22"/>
+                <c:pt idx="0">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6250</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8750</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>11250</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13750</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12749</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11747</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10746</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9744</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8743</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7741</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>6740</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5738</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4737</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3735</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2734</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1732</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>731</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B144-412D-A091-CD215F21A09C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="427888024"/>
+        <c:axId val="427885400"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="427888024"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="427885400"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="427885400"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="427888024"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -2195,6 +2410,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
@@ -3743,27 +3998,543 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>371474</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEF337E8-841D-40B3-9330-C07FBEB181B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEDB543D-08F7-46C1-8892-B92C9A4D0CF6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3788,23 +4559,66 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>518160</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>95249</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>213360</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>371474</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39EB2A35-EA5F-4195-B1C3-1D5D38C67DC1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2DDC85D-9AE7-4B4D-92BB-BFC60A947925}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>142874</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>114299</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{668617EC-A16C-42B6-BFB5-F515C870943E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3825,27 +4639,27 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>114299</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
+      <xdr:rowOff>152399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D183E8AC-ECB0-4F57-B91B-81DE89F1EB97}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F7AAE32B-AFB6-4490-8243-7C59A9FD04B8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4162,712 +4976,312 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFF8627F-FBA7-4089-B749-5F88DEE9C904}">
-  <dimension ref="A1:B88"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B1">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B2">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1118</v>
+      </c>
+      <c r="C2">
+        <f>B2-B1</f>
+        <v>1118</v>
+      </c>
+      <c r="D2">
+        <f>A2-A1</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="B3">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2236</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C16" si="0">B3-B2</f>
+        <v>1118</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D16" si="1">A3-A2</f>
+        <v>105</v>
+      </c>
+      <c r="E3">
+        <f>D3-D2</f>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>156</v>
+        <v>314</v>
       </c>
       <c r="B4">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3354</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>175</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E16" si="2">D4-D3</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
+        <v>559</v>
+      </c>
+      <c r="B5">
+        <v>4472</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>245</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>873</v>
+      </c>
+      <c r="B6">
+        <v>5590</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>314</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="2"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1257</v>
+      </c>
+      <c r="B7">
+        <v>6708</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>384</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1711</v>
+      </c>
+      <c r="B8">
+        <v>7826</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>454</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2288</v>
+      </c>
+      <c r="B9">
+        <v>7827</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>577</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2742</v>
+      </c>
+      <c r="B10">
+        <v>6709</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>454</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>-123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>3126</v>
+      </c>
+      <c r="B11">
+        <v>5591</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>384</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="2"/>
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>3441</v>
+      </c>
+      <c r="B12">
+        <v>4473</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>315</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>-69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>3685</v>
+      </c>
+      <c r="B13">
+        <v>3355</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
         <v>244</v>
       </c>
-      <c r="B5">
-        <v>3125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>351</v>
-      </c>
-      <c r="B6">
-        <v>3750</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>478</v>
-      </c>
-      <c r="B7">
-        <v>4375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>625</v>
-      </c>
-      <c r="B8">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>791</v>
-      </c>
-      <c r="B9">
-        <v>5625</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>976</v>
-      </c>
-      <c r="B10">
-        <v>6250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1181</v>
-      </c>
-      <c r="B11">
-        <v>6875</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>1406</v>
-      </c>
-      <c r="B12">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>1650</v>
-      </c>
-      <c r="B13">
-        <v>8125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="E13">
+        <f t="shared" si="2"/>
+        <v>-71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>1914</v>
+        <v>3860</v>
       </c>
       <c r="B14">
-        <v>8750</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2237</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>175</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="2"/>
+        <v>-69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2197</v>
+        <v>3965</v>
       </c>
       <c r="B15">
-        <v>9375</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1119</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="B16">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>2822</v>
-      </c>
-      <c r="B17">
-        <v>10625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>3164</v>
-      </c>
-      <c r="B18">
-        <v>11250</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>3525</v>
-      </c>
-      <c r="B19">
-        <v>11875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>3906</v>
-      </c>
-      <c r="B20">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>4306</v>
-      </c>
-      <c r="B21">
-        <v>13125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>4726</v>
-      </c>
-      <c r="B22">
-        <v>13750</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>5166</v>
-      </c>
-      <c r="B23">
-        <v>14375</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>5625</v>
-      </c>
-      <c r="B24">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>6093</v>
-      </c>
-      <c r="B25">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>6562</v>
-      </c>
-      <c r="B26">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>7031</v>
-      </c>
-      <c r="B27">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>7500</v>
-      </c>
-      <c r="B28">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>7968</v>
-      </c>
-      <c r="B29">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>8437</v>
-      </c>
-      <c r="B30">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>8906</v>
-      </c>
-      <c r="B31">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>9375</v>
-      </c>
-      <c r="B32">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>9843</v>
-      </c>
-      <c r="B33">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>10312</v>
-      </c>
-      <c r="B34">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>10781</v>
-      </c>
-      <c r="B35">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>11250</v>
-      </c>
-      <c r="B36">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>11718</v>
-      </c>
-      <c r="B37">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>12187</v>
-      </c>
-      <c r="B38">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>12656</v>
-      </c>
-      <c r="B39">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>13125</v>
-      </c>
-      <c r="B40">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>13593</v>
-      </c>
-      <c r="B41">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>14062</v>
-      </c>
-      <c r="B42">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>14531</v>
-      </c>
-      <c r="B43">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>15000</v>
-      </c>
-      <c r="B44">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45">
-        <v>15468</v>
-      </c>
-      <c r="B45">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46">
-        <v>15937</v>
-      </c>
-      <c r="B46">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47">
-        <v>16406</v>
-      </c>
-      <c r="B47">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48">
-        <v>16875</v>
-      </c>
-      <c r="B48">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>17343</v>
-      </c>
-      <c r="B49">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>17812</v>
-      </c>
-      <c r="B50">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>18281</v>
-      </c>
-      <c r="B51">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>18750</v>
-      </c>
-      <c r="B52">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>19218</v>
-      </c>
-      <c r="B53">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>19687</v>
-      </c>
-      <c r="B54">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55">
-        <v>20156</v>
-      </c>
-      <c r="B55">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56">
-        <v>20625</v>
-      </c>
-      <c r="B56">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>21093</v>
-      </c>
-      <c r="B57">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>21562</v>
-      </c>
-      <c r="B58">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>22031</v>
-      </c>
-      <c r="B59">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>22500</v>
-      </c>
-      <c r="B60">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61">
-        <v>22968</v>
-      </c>
-      <c r="B61">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62">
-        <v>23437</v>
-      </c>
-      <c r="B62">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63">
-        <v>23906</v>
-      </c>
-      <c r="B63">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64">
-        <v>24375</v>
-      </c>
-      <c r="B64">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65">
-        <v>24833</v>
-      </c>
-      <c r="B65">
-        <v>14375</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66">
-        <v>25273</v>
-      </c>
-      <c r="B66">
-        <v>13750</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67">
-        <v>25693</v>
-      </c>
-      <c r="B67">
-        <v>13125</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68">
-        <v>26093</v>
-      </c>
-      <c r="B68">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69">
-        <v>26474</v>
-      </c>
-      <c r="B69">
-        <v>11875</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70">
-        <v>26835</v>
-      </c>
-      <c r="B70">
-        <v>11250</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71">
-        <v>27177</v>
-      </c>
-      <c r="B71">
-        <v>10625</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72">
-        <v>27500</v>
-      </c>
-      <c r="B72">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73">
-        <v>27802</v>
-      </c>
-      <c r="B73">
-        <v>9375</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74">
-        <v>28085</v>
-      </c>
-      <c r="B74">
-        <v>8750</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75">
-        <v>28349</v>
-      </c>
-      <c r="B75">
-        <v>8125</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76">
-        <v>28593</v>
-      </c>
-      <c r="B76">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77">
-        <v>28818</v>
-      </c>
-      <c r="B77">
-        <v>6875</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78">
-        <v>29023</v>
-      </c>
-      <c r="B78">
-        <v>6250</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79">
-        <v>29208</v>
-      </c>
-      <c r="B79">
-        <v>5625</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80">
-        <v>29375</v>
-      </c>
-      <c r="B80">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81">
-        <v>29521</v>
-      </c>
-      <c r="B81">
-        <v>4375</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82">
-        <v>29648</v>
-      </c>
-      <c r="B82">
-        <v>3750</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83">
-        <v>29755</v>
-      </c>
-      <c r="B83">
-        <v>3125</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84">
-        <v>29843</v>
-      </c>
-      <c r="B84">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85">
-        <v>29912</v>
-      </c>
-      <c r="B85">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86">
-        <v>29960</v>
-      </c>
-      <c r="B86">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87">
-        <v>29990</v>
-      </c>
-      <c r="B87">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88">
-        <v>30000</v>
-      </c>
-      <c r="B88">
         <v>0</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>-1119</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>-70</v>
       </c>
     </row>
   </sheetData>
@@ -4877,360 +5291,518 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09DA11A3-FB0E-49A5-8DDD-7886764BC416}">
-  <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B1">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="B2">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2236</v>
+      </c>
+      <c r="C2">
+        <f>B2-B1</f>
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>351</v>
+        <v>314</v>
       </c>
       <c r="B3">
-        <v>3750</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3354</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C15" si="0">B3-B2</f>
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>625</v>
+        <v>559</v>
       </c>
       <c r="B4">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4472</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>976</v>
+        <v>873</v>
       </c>
       <c r="B5">
-        <v>6250</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5590</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1406</v>
+        <v>1257</v>
       </c>
       <c r="B6">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6708</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1914</v>
+        <v>1711</v>
       </c>
       <c r="B7">
-        <v>8750</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7826</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2500</v>
+        <v>2236</v>
       </c>
       <c r="B8">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>8945</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>3164</v>
+        <v>2760</v>
       </c>
       <c r="B9">
-        <v>11250</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+        <v>7827</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>3906</v>
+        <v>3214</v>
       </c>
       <c r="B10">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6709</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>4726</v>
+        <v>3598</v>
       </c>
       <c r="B11">
-        <v>13750</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5591</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>5625</v>
+        <v>3913</v>
       </c>
       <c r="B12">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>4473</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>6562</v>
+        <v>4157</v>
       </c>
       <c r="B13">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>3355</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>7500</v>
+        <v>4332</v>
       </c>
       <c r="B14">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>2237</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>8437</v>
+        <v>4000</v>
       </c>
       <c r="B15">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>-2237</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2">
+        <v>1118</v>
+      </c>
+      <c r="C2">
+        <f>B2-B1</f>
+        <v>1118</v>
+      </c>
+      <c r="D2">
+        <f>A2-A1</f>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>139</v>
+      </c>
+      <c r="B3">
+        <v>2236</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C17" si="0">B3-B2</f>
+        <v>1118</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D16" si="1">A3-A2</f>
+        <v>105</v>
+      </c>
+      <c r="E3">
+        <f>D3-D2</f>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>314</v>
+      </c>
+      <c r="B4">
+        <v>3354</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>175</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E17" si="2">D4-D3</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>559</v>
+      </c>
+      <c r="B5">
+        <v>4472</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>245</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>873</v>
+      </c>
+      <c r="B6">
+        <v>5590</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>314</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="2"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1257</v>
+      </c>
+      <c r="B7">
+        <v>6708</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>384</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1711</v>
+      </c>
+      <c r="B8">
+        <v>7826</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>1118</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>454</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1764</v>
+      </c>
+      <c r="B9">
+        <v>8945</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>1119</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="2"/>
+        <v>-401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2288</v>
+      </c>
+      <c r="B10">
+        <v>7827</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>524</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="2"/>
+        <v>471</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>2742</v>
+      </c>
+      <c r="B11">
+        <v>6709</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>454</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="2"/>
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>3126</v>
+      </c>
+      <c r="B12">
+        <v>5591</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>384</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>3441</v>
+      </c>
+      <c r="B13">
+        <v>4473</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>315</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="2"/>
+        <v>-69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>3685</v>
+      </c>
+      <c r="B14">
+        <v>3355</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>244</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="2"/>
+        <v>-71</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>3860</v>
+      </c>
+      <c r="B15">
+        <v>2237</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>175</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="2"/>
+        <v>-69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>9375</v>
+        <v>3965</v>
       </c>
       <c r="B16">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>1119</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>-1118</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="2"/>
+        <v>-70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>10312</v>
+        <v>4000</v>
       </c>
       <c r="B17">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>11250</v>
-      </c>
-      <c r="B18">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>12187</v>
-      </c>
-      <c r="B19">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>13125</v>
-      </c>
-      <c r="B20">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>14062</v>
-      </c>
-      <c r="B21">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>15000</v>
-      </c>
-      <c r="B22">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>15937</v>
-      </c>
-      <c r="B23">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>16875</v>
-      </c>
-      <c r="B24">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>17812</v>
-      </c>
-      <c r="B25">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>18750</v>
-      </c>
-      <c r="B26">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
-        <v>19687</v>
-      </c>
-      <c r="B27">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
-        <v>20625</v>
-      </c>
-      <c r="B28">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
-        <v>21562</v>
-      </c>
-      <c r="B29">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>22500</v>
-      </c>
-      <c r="B30">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
-        <v>23437</v>
-      </c>
-      <c r="B31">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
-        <v>24375</v>
-      </c>
-      <c r="B32">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
-        <v>25273</v>
-      </c>
-      <c r="B33">
-        <v>13750</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
-        <v>26093</v>
-      </c>
-      <c r="B34">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
-        <v>26835</v>
-      </c>
-      <c r="B35">
-        <v>11250</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36">
-        <v>27500</v>
-      </c>
-      <c r="B36">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37">
-        <v>28085</v>
-      </c>
-      <c r="B37">
-        <v>8750</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38">
-        <v>28593</v>
-      </c>
-      <c r="B38">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39">
-        <v>29023</v>
-      </c>
-      <c r="B39">
-        <v>6250</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40">
-        <v>29375</v>
-      </c>
-      <c r="B40">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41">
-        <v>29648</v>
-      </c>
-      <c r="B41">
-        <v>3750</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>29843</v>
-      </c>
-      <c r="B42">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43">
-        <v>29960</v>
-      </c>
-      <c r="B43">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44">
-        <v>30000</v>
-      </c>
-      <c r="B44">
         <v>0</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>-1119</v>
+      </c>
+      <c r="D17">
+        <f t="shared" ref="D17" si="3">A17-A16</f>
+        <v>35</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="2"/>
+        <v>-70</v>
       </c>
     </row>
   </sheetData>
@@ -5239,533 +5811,889 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FF1BB8E-06C8-45E3-A3C1-FA6B715D31B1}">
-  <dimension ref="A1:C44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>39</v>
+      </c>
+      <c r="B3">
+        <v>1250</v>
+      </c>
+      <c r="C3">
+        <f>A3-A2</f>
+        <v>39</v>
+      </c>
+      <c r="E3">
+        <f>B3-B2</f>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>156</v>
+      </c>
+      <c r="B4">
+        <v>2500</v>
+      </c>
+      <c r="C4">
+        <f>A4-A3</f>
+        <v>117</v>
+      </c>
+      <c r="D4">
+        <f>C4-C3</f>
+        <v>78</v>
+      </c>
+      <c r="E4">
+        <f>B4-B3</f>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>351</v>
+      </c>
+      <c r="B5">
+        <v>3750</v>
+      </c>
+      <c r="C5">
+        <f>A5-A4</f>
+        <v>195</v>
+      </c>
+      <c r="D5">
+        <f>C5-C4</f>
+        <v>78</v>
+      </c>
+      <c r="E5">
+        <f>B5-B4</f>
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>586</v>
+      </c>
+      <c r="B6">
+        <v>3750</v>
+      </c>
+      <c r="C6">
+        <f>A6-A5</f>
+        <v>235</v>
+      </c>
+      <c r="D6">
+        <f>C6-C5</f>
+        <v>40</v>
+      </c>
+      <c r="E6">
+        <f>B6-B5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>781</v>
+      </c>
+      <c r="B7">
+        <v>2500</v>
+      </c>
+      <c r="C7">
+        <f>A7-A6</f>
+        <v>195</v>
+      </c>
+      <c r="D7">
+        <f>C7-C6</f>
+        <v>-40</v>
+      </c>
+      <c r="E7">
+        <f>B7-B6</f>
+        <v>-1250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>898</v>
+      </c>
+      <c r="B8">
+        <v>1250</v>
+      </c>
+      <c r="C8">
+        <f>A8-A7</f>
+        <v>117</v>
+      </c>
+      <c r="D8">
+        <f>C8-C7</f>
+        <v>-78</v>
+      </c>
+      <c r="E8">
+        <f>B8-B7</f>
+        <v>-1250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1000</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f>A9-A8</f>
+        <v>102</v>
+      </c>
+      <c r="D9">
+        <f>C9-C8</f>
+        <v>-15</v>
+      </c>
+      <c r="E9">
+        <f>B9-B8</f>
+        <v>-1250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>39</v>
+        <v>10000</v>
       </c>
       <c r="B1">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>156</v>
+        <v>10351</v>
       </c>
       <c r="B2">
-        <v>2500</v>
+        <v>6250</v>
       </c>
       <c r="C2">
         <f>A2-A1</f>
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>351</v>
+        <v>10781</v>
       </c>
       <c r="B3">
-        <v>3750</v>
+        <v>7500</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C44" si="0">A3-A2</f>
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" ref="C3:C23" si="0">A3-A2</f>
+        <v>430</v>
+      </c>
+      <c r="D3">
+        <f>C3-C2</f>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>625</v>
+        <v>11289</v>
       </c>
       <c r="B4">
-        <v>5000</v>
+        <v>8750</v>
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
-        <v>274</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>508</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D45" si="1">C4-C3</f>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>976</v>
+        <v>11875</v>
       </c>
       <c r="B5">
-        <v>6250</v>
+        <v>10000</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
-        <v>351</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+        <v>586</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1406</v>
+        <v>12539</v>
       </c>
       <c r="B6">
-        <v>7500</v>
+        <v>11250</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
-        <v>430</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+        <v>664</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1914</v>
+        <v>13281</v>
       </c>
       <c r="B7">
-        <v>8750</v>
+        <v>12500</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
-        <v>508</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+        <v>742</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2500</v>
+        <v>14101</v>
       </c>
       <c r="B8">
-        <v>10000</v>
+        <v>13750</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
-        <v>586</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+        <v>820</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>3164</v>
+        <v>14929</v>
       </c>
       <c r="B9">
-        <v>11250</v>
+        <v>12749</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
-        <v>664</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+        <v>828</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>3906</v>
+        <v>15695</v>
       </c>
       <c r="B10">
-        <v>12500</v>
+        <v>11747</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
-        <v>742</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+        <v>766</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="1"/>
+        <v>-62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>4726</v>
+        <v>16398</v>
       </c>
       <c r="B11">
-        <v>13750</v>
+        <v>10746</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
-        <v>820</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+        <v>703</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="1"/>
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>5625</v>
+        <v>17038</v>
       </c>
       <c r="B12">
-        <v>15000</v>
+        <v>9744</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
-        <v>899</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+        <v>640</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="1"/>
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>6562</v>
+        <v>17616</v>
       </c>
       <c r="B13">
-        <v>15000</v>
+        <v>8743</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
-        <v>937</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+        <v>578</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="1"/>
+        <v>-62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>7500</v>
+        <v>18131</v>
       </c>
       <c r="B14">
-        <v>15000</v>
+        <v>7741</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
-        <v>938</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+        <v>515</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>8437</v>
+        <v>18583</v>
       </c>
       <c r="B15">
-        <v>15000</v>
+        <v>6740</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
-        <v>937</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+        <v>452</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="1"/>
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>9375</v>
+        <v>18973</v>
       </c>
       <c r="B16">
-        <v>15000</v>
+        <v>5738</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
-        <v>938</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>390</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="1"/>
+        <v>-62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>10312</v>
+        <v>19301</v>
       </c>
       <c r="B17">
-        <v>15000</v>
+        <v>4737</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
-        <v>937</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>328</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>-62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>11250</v>
+        <v>19565</v>
       </c>
       <c r="B18">
-        <v>15000</v>
+        <v>3735</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
-        <v>938</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>264</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>-64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>12187</v>
+        <v>19767</v>
       </c>
       <c r="B19">
-        <v>15000</v>
+        <v>2734</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
-        <v>937</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>-62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>13125</v>
+        <v>19907</v>
       </c>
       <c r="B20">
-        <v>15000</v>
+        <v>1732</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
-        <v>938</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>-62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>14062</v>
+        <v>19984</v>
       </c>
       <c r="B21">
-        <v>15000</v>
+        <v>731</v>
       </c>
       <c r="C21">
         <f t="shared" si="0"/>
-        <v>937</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>-63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="B22">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="C22">
         <f t="shared" si="0"/>
-        <v>938</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>-61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>15937</v>
+        <v>15000</v>
       </c>
       <c r="B23">
         <v>15000</v>
       </c>
       <c r="C23">
         <f t="shared" si="0"/>
-        <v>937</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>-5000</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>-5016</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>16875</v>
+        <v>15937</v>
       </c>
       <c r="B24">
         <v>15000</v>
       </c>
       <c r="C24">
-        <f t="shared" si="0"/>
-        <v>938</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" ref="C24:C25" si="2">A24-A23</f>
+        <v>937</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>5937</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>17812</v>
+        <v>16875</v>
       </c>
       <c r="B25">
         <v>15000</v>
       </c>
       <c r="C25">
-        <f t="shared" si="0"/>
-        <v>937</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" si="2"/>
+        <v>938</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>18750</v>
+        <v>17812</v>
       </c>
       <c r="B26">
         <v>15000</v>
       </c>
       <c r="C26">
-        <f t="shared" si="0"/>
-        <v>938</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" ref="C26:C35" si="3">A26-A25</f>
+        <v>937</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>19687</v>
+        <v>18750</v>
       </c>
       <c r="B27">
         <v>15000</v>
       </c>
       <c r="C27">
-        <f t="shared" si="0"/>
-        <v>937</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>938</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>20625</v>
+        <v>19687</v>
       </c>
       <c r="B28">
         <v>15000</v>
       </c>
       <c r="C28">
-        <f t="shared" si="0"/>
-        <v>938</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>937</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>21562</v>
+        <v>20625</v>
       </c>
       <c r="B29">
         <v>15000</v>
       </c>
       <c r="C29">
-        <f t="shared" si="0"/>
-        <v>937</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>938</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>22500</v>
+        <v>21562</v>
       </c>
       <c r="B30">
         <v>15000</v>
       </c>
       <c r="C30">
-        <f t="shared" si="0"/>
-        <v>938</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>937</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>23437</v>
+        <v>22500</v>
       </c>
       <c r="B31">
         <v>15000</v>
       </c>
       <c r="C31">
-        <f t="shared" si="0"/>
-        <v>937</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <f t="shared" si="3"/>
+        <v>938</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>24375</v>
+        <v>23437</v>
       </c>
       <c r="B32">
         <v>15000</v>
       </c>
       <c r="C32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
+        <v>937</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>24375</v>
+      </c>
+      <c r="B33">
+        <v>15000</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="3"/>
         <v>938</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="D33">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>25273</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>13750</v>
       </c>
-      <c r="C33">
-        <f t="shared" si="0"/>
+      <c r="C34">
+        <f t="shared" si="3"/>
         <v>898</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="D34">
+        <f t="shared" si="1"/>
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>26093</v>
       </c>
-      <c r="B34">
+      <c r="B35">
         <v>12500</v>
       </c>
-      <c r="C34">
-        <f t="shared" si="0"/>
+      <c r="C35">
+        <f t="shared" si="3"/>
         <v>820</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="D35">
+        <f t="shared" si="1"/>
+        <v>-78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>26835</v>
       </c>
-      <c r="B35">
+      <c r="B36">
         <v>11250</v>
       </c>
-      <c r="C35">
-        <f t="shared" si="0"/>
+      <c r="C36">
+        <f t="shared" ref="C36:C45" si="4">A36-A35</f>
         <v>742</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36">
+      <c r="D36">
+        <f t="shared" si="1"/>
+        <v>-78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>27500</v>
       </c>
-      <c r="B36">
+      <c r="B37">
         <v>10000</v>
       </c>
-      <c r="C36">
-        <f t="shared" si="0"/>
+      <c r="C37">
+        <f t="shared" si="4"/>
         <v>665</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37">
+      <c r="D37">
+        <f t="shared" si="1"/>
+        <v>-77</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>28085</v>
       </c>
-      <c r="B37">
+      <c r="B38">
         <v>8750</v>
       </c>
-      <c r="C37">
-        <f t="shared" si="0"/>
+      <c r="C38">
+        <f t="shared" si="4"/>
         <v>585</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38">
+      <c r="D38">
+        <f t="shared" si="1"/>
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
         <v>28593</v>
       </c>
-      <c r="B38">
+      <c r="B39">
         <v>7500</v>
       </c>
-      <c r="C38">
-        <f t="shared" si="0"/>
+      <c r="C39">
+        <f t="shared" si="4"/>
         <v>508</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39">
+      <c r="D39">
+        <f t="shared" si="1"/>
+        <v>-77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>29023</v>
       </c>
-      <c r="B39">
+      <c r="B40">
         <v>6250</v>
       </c>
-      <c r="C39">
-        <f t="shared" si="0"/>
+      <c r="C40">
+        <f t="shared" ref="C40:C45" si="5">A40-A39</f>
         <v>430</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40">
+      <c r="D40">
+        <f t="shared" si="1"/>
+        <v>-78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>29375</v>
       </c>
-      <c r="B40">
+      <c r="B41">
         <v>5000</v>
       </c>
-      <c r="C40">
-        <f t="shared" si="0"/>
+      <c r="C41">
+        <f t="shared" si="5"/>
         <v>352</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41">
+      <c r="D41">
+        <f t="shared" si="1"/>
+        <v>-78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>29648</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <v>3750</v>
       </c>
-      <c r="C41">
-        <f t="shared" si="0"/>
+      <c r="C42">
+        <f t="shared" si="5"/>
         <v>273</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42">
+      <c r="D42">
+        <f t="shared" si="1"/>
+        <v>-79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>29843</v>
       </c>
-      <c r="B42">
+      <c r="B43">
         <v>2500</v>
       </c>
-      <c r="C42">
-        <f t="shared" si="0"/>
+      <c r="C43">
+        <f t="shared" si="5"/>
         <v>195</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43">
+      <c r="D43">
+        <f t="shared" si="1"/>
+        <v>-78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>29960</v>
       </c>
-      <c r="B43">
+      <c r="B44">
         <v>1250</v>
       </c>
-      <c r="C43">
-        <f t="shared" si="0"/>
+      <c r="C44">
+        <f t="shared" si="5"/>
         <v>117</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44">
+      <c r="D44">
+        <f t="shared" si="1"/>
+        <v>-78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>30000</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>0</v>
       </c>
-      <c r="C44">
-        <f t="shared" si="0"/>
+      <c r="C45">
+        <f t="shared" si="5"/>
         <v>40</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="1"/>
+        <v>-77</v>
       </c>
     </row>
   </sheetData>
